--- a/resources/protocols/G0241_19_D.xlsx
+++ b/resources/protocols/G0241_19_D.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="50">
   <si>
     <t xml:space="preserve">number_availible_animals</t>
   </si>
@@ -168,13 +168,10 @@
     <t xml:space="preserve">AAV-GCAMP6-DIO</t>
   </si>
   <si>
-    <t xml:space="preserve">users</t>
-  </si>
-  <si>
     <t xml:space="preserve">operative?</t>
   </si>
   <si>
-    <t xml:space="preserve">Maristany Eduardo </t>
+    <t xml:space="preserve">Maristany Eduardo</t>
   </si>
   <si>
     <t xml:space="preserve">Jan van Dick</t>
@@ -188,7 +185,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -218,12 +215,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -282,8 +273,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -307,7 +302,7 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -331,16 +326,16 @@
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.79"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>10</v>
       </c>
     </row>
@@ -363,201 +358,201 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="59.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="59.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21.56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="0" t="n">
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="0" t="n">
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="0" t="s">
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="0" t="n">
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="0" t="n">
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D6" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="0" t="s">
+      <c r="D6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="0" t="n">
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="0" t="s">
+      <c r="D7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" s="0" t="n">
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="0" t="n">
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="0" t="s">
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="0" t="n">
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="0" t="n">
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -580,122 +575,122 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="17.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="25.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="17.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="25.44"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="0" t="n">
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="0" t="n">
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="0" t="n">
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="0" t="n">
+      <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="0" t="s">
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -718,38 +713,38 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="11.5625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.44"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="0" t="s">
+      <c r="B1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="0" t="n">
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1"/>
+      <c r="A3" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -770,62 +765,62 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="11.5625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28.37"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" s="0" t="n">
+      <c r="B2" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="0" t="n">
+      <c r="B3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="0" t="n">
+      <c r="B4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="0" t="n">
+      <c r="B5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -848,30 +843,30 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="0" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/resources/protocols/G0241_19_D.xlsx
+++ b/resources/protocols/G0241_19_D.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" state="visible" r:id="rId2"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="49">
   <si>
     <t xml:space="preserve">number_availible_animals</t>
   </si>
@@ -145,9 +145,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.66x units</t>
-  </si>
-  <si>
-    <t xml:space="preserve">days after start</t>
   </si>
   <si>
     <t xml:space="preserve">duration</t>
@@ -723,15 +720,15 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -782,7 +779,7 @@
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>2</v>
@@ -793,7 +790,7 @@
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>2</v>
@@ -804,7 +801,7 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>2</v>
@@ -815,7 +812,7 @@
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>2</v>
@@ -851,12 +848,12 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -864,7 +861,7 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>9</v>
